--- a/data/pack/us/vacuno_vivo_us.xlsx
+++ b/data/pack/us/vacuno_vivo_us.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K435"/>
+  <dimension ref="A1:K434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,11 +512,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>187.55</v>
+        <v>186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -567,11 +567,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>185.99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>186</v>
+        <v>187.56</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185.99</v>
+        <v>187.84</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>187.56</v>
+        <v>187</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>187.84</v>
+        <v>186.97</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>187</v>
+        <v>186.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -897,11 +897,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>186.97</v>
+        <v>190.14</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -952,11 +952,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>186.5</v>
+        <v>190.18</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1007,11 +1007,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>190.14</v>
+        <v>189.47</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>190.18</v>
+        <v>189.92</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>189.47</v>
+        <v>189.88</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1172,11 +1172,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>189.92</v>
+        <v>190.11</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>189.88</v>
+        <v>188.24</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>190.11</v>
+        <v>186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1337,11 +1337,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>188.24</v>
+        <v>184</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>186.78</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>184</v>
+        <v>186.55</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1502,11 +1502,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>186.78</v>
+        <v>185.51</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1557,11 +1557,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>186.55</v>
+        <v>184.84</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185.51</v>
+        <v>184.71</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>184.84</v>
+        <v>184.95</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1722,11 +1722,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>184.71</v>
+        <v>184.97</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1777,11 +1777,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>184.95</v>
+        <v>185.71</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>184.97</v>
+        <v>187.12</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1887,11 +1887,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185.71</v>
+        <v>187.87</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>187.12</v>
+        <v>186.39</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1997,11 +1997,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>187.87</v>
+        <v>190.05</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>186.39</v>
+        <v>190</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>190.05</v>
+        <v>190</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2217,11 +2217,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>190</v>
+        <v>190.07</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>190</v>
+        <v>190.28</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>190.07</v>
+        <v>191.32</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2382,11 +2382,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>190.28</v>
+        <v>190.95</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>191.32</v>
+        <v>190.88</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2492,11 +2492,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>190.95</v>
+        <v>193.88</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>190.88</v>
+        <v>195.05</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>193.88</v>
+        <v>194.66</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>195.05</v>
+        <v>195.29</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>194.66</v>
+        <v>191.43</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2767,11 +2767,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>195.29</v>
+        <v>194.78</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2822,11 +2822,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>191.43</v>
+        <v>194.67</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2877,11 +2877,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>194.78</v>
+        <v>193.14</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>194.67</v>
+        <v>190.91</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2987,11 +2987,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>193.14</v>
+        <v>190.55</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3042,11 +3042,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>190.91</v>
+        <v>194.71</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>190.55</v>
+        <v>192</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3152,11 +3152,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>194.71</v>
+        <v>193.46</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3207,11 +3207,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>192</v>
+        <v>196.9</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3262,11 +3262,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>193.46</v>
+        <v>199.58</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3317,11 +3317,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>196.9</v>
+        <v>199.84</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>199.58</v>
+        <v>196.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>199.84</v>
+        <v>199.64</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3482,11 +3482,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>196.5</v>
+        <v>202.43</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3537,11 +3537,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>199.64</v>
+        <v>202.15</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3592,11 +3592,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>202.43</v>
+        <v>202.93</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>202.15</v>
+        <v>203.92</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3702,11 +3702,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>202.93</v>
+        <v>201.37</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3757,11 +3757,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>203.92</v>
+        <v>203.76</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3812,11 +3812,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>201.37</v>
+        <v>203.91</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3867,11 +3867,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>203.76</v>
+        <v>201</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>203.91</v>
+        <v>201.2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>201</v>
+        <v>203.38</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>201.2</v>
+        <v>206.65</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4087,11 +4087,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>203.38</v>
+        <v>210.36</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4142,11 +4142,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>206.65</v>
+        <v>203</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>210.36</v>
+        <v>202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>203</v>
+        <v>208.8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>202</v>
+        <v>209.16</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4362,11 +4362,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>208.8</v>
+        <v>209.92</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4417,11 +4417,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>209.16</v>
+        <v>208</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>209.92</v>
+        <v>206.85</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4527,11 +4527,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>208</v>
+        <v>206.98</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4582,11 +4582,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>206.85</v>
+        <v>205.11</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4637,11 +4637,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>206.98</v>
+        <v>204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4692,11 +4692,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>205.11</v>
+        <v>202.97</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>204</v>
+        <v>202.81</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4802,11 +4802,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>202.97</v>
+        <v>202.82</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>202.81</v>
+        <v>202.97</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4912,11 +4912,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>202.82</v>
+        <v>203</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>202.97</v>
+        <v>200</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5077,11 +5077,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>200</v>
+        <v>199.54</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5132,11 +5132,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>200</v>
+        <v>199.46</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>199.54</v>
+        <v>197</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>199.46</v>
+        <v>198</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>197</v>
+        <v>197.58</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5352,11 +5352,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5407,11 +5407,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>197.58</v>
+        <v>196.38</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>195</v>
+        <v>196.41</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5517,11 +5517,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>196.38</v>
+        <v>196.84</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>196.41</v>
+        <v>201.09</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>196.84</v>
+        <v>199.59</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5682,11 +5682,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>201.09</v>
+        <v>200</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5737,11 +5737,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>199.59</v>
+        <v>205.04</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5792,11 +5792,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5847,11 +5847,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>205.04</v>
+        <v>209.42</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5902,11 +5902,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>202</v>
+        <v>212.49</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5957,11 +5957,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>209.42</v>
+        <v>207.78</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -6012,11 +6012,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>212.49</v>
+        <v>212.21</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -6067,11 +6067,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>207.78</v>
+        <v>212.23</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6122,11 +6122,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>212.21</v>
+        <v>211.83</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6177,11 +6177,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>212.23</v>
+        <v>210</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6232,11 +6232,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>211.83</v>
+        <v>210</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6287,11 +6287,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>210</v>
+        <v>211.96</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6342,11 +6342,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>210</v>
+        <v>210.04</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6397,11 +6397,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>211.96</v>
+        <v>204.25</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6452,11 +6452,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>210.04</v>
+        <v>207.58</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6507,11 +6507,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>204.25</v>
+        <v>207.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6562,11 +6562,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>207.58</v>
+        <v>207.57</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6617,11 +6617,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>207.5</v>
+        <v>206.79</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>207.57</v>
+        <v>208</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>206.79</v>
+        <v>208</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6782,11 +6782,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>208</v>
+        <v>211.19</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6837,11 +6837,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>208</v>
+        <v>212.28</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6892,11 +6892,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>211.19</v>
+        <v>208.52</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6947,11 +6947,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>212.28</v>
+        <v>212.55</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -7002,11 +7002,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>208.52</v>
+        <v>210.08</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -7057,11 +7057,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>212.55</v>
+        <v>216.03</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -7112,11 +7112,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>210.08</v>
+        <v>214.23</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -7167,11 +7167,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>216.03</v>
+        <v>220.65</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -7222,11 +7222,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>214.23</v>
+        <v>221.2</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -7277,11 +7277,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220.65</v>
+        <v>219.25</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -7332,11 +7332,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221.2</v>
+        <v>219.08</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -7387,11 +7387,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219.25</v>
+        <v>218.47</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -7442,11 +7442,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219.08</v>
+        <v>219.97</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -7497,11 +7497,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>218.47</v>
+        <v>226.36</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -7552,11 +7552,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219.97</v>
+        <v>226.56</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -7607,11 +7607,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>226.36</v>
+        <v>225</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -7662,11 +7662,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>226.56</v>
+        <v>227.25</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -7717,11 +7717,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>225</v>
+        <v>225.93</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>227.25</v>
+        <v>226.39</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -7827,11 +7827,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>225.93</v>
+        <v>219</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -7882,11 +7882,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>226.39</v>
+        <v>219</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -7937,11 +7937,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219</v>
+        <v>230.05</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -8047,11 +8047,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>230</v>
+        <v>223.15</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -8102,11 +8102,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>230.05</v>
+        <v>229.84</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -8157,11 +8157,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>223.15</v>
+        <v>220.83</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -8212,11 +8212,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229.84</v>
+        <v>229.25</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -8267,11 +8267,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220.83</v>
+        <v>234.35</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -8322,11 +8322,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229.25</v>
+        <v>230</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -8377,11 +8377,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>234.35</v>
+        <v>236</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -8432,11 +8432,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>230</v>
+        <v>226.85</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -8487,11 +8487,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>236</v>
+        <v>237.04</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -8542,11 +8542,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>226.85</v>
+        <v>239.51</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -8597,11 +8597,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>237.04</v>
+        <v>236.43</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -8652,11 +8652,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>239.51</v>
+        <v>234.76</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -8707,11 +8707,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>236.43</v>
+        <v>237.19</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -8762,11 +8762,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>234.76</v>
+        <v>237.11</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -8817,11 +8817,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>237.19</v>
+        <v>240.13</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -8872,11 +8872,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>237.11</v>
+        <v>239.47</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -8927,11 +8927,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>240.13</v>
+        <v>233.17</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -8982,11 +8982,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>239.47</v>
+        <v>236.42</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -9037,11 +9037,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>233.17</v>
+        <v>235.55</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -9092,11 +9092,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>236.42</v>
+        <v>231.54</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -9147,11 +9147,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>235.55</v>
+        <v>230.08</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -9202,11 +9202,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>231.54</v>
+        <v>230.49</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>230.08</v>
+        <v>227.19</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -9312,11 +9312,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>230.49</v>
+        <v>231.07</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -9367,11 +9367,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>227.19</v>
+        <v>231.99</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -9422,11 +9422,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>231.07</v>
+        <v>222.55</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -9477,11 +9477,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>231.99</v>
+        <v>229.11</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -9532,11 +9532,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>222.55</v>
+        <v>229.66</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -9587,11 +9587,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>229.11</v>
+        <v>225.28</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -9642,11 +9642,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229.66</v>
+        <v>235.08</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -9697,11 +9697,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>225.28</v>
+        <v>237.52</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -9752,11 +9752,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>235.08</v>
+        <v>234</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -9807,11 +9807,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>237.52</v>
+        <v>233.67</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -9862,11 +9862,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>234</v>
+        <v>233.77</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -9917,11 +9917,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>233.67</v>
+        <v>236.13</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -9972,11 +9972,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>233.77</v>
+        <v>239.19</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -10027,11 +10027,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>236.13</v>
+        <v>238.88</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -10082,11 +10082,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>239.19</v>
+        <v>230.28</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -10137,11 +10137,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>238.88</v>
+        <v>231.04</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -10192,11 +10192,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>230.28</v>
+        <v>239.36</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -10247,11 +10247,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>231.04</v>
+        <v>230</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -10302,11 +10302,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>239.36</v>
+        <v>240</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -10357,11 +10357,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>230</v>
+        <v>235.6</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -10412,11 +10412,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>240</v>
+        <v>242.38</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -10467,11 +10467,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>235.6</v>
+        <v>243.69</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -10522,11 +10522,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>242.38</v>
+        <v>240</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -10577,11 +10577,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>243.69</v>
+        <v>240</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -10632,11 +10632,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -10687,11 +10687,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>240</v>
+        <v>240.1</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -10742,11 +10742,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>237</v>
+        <v>241.06</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -10797,11 +10797,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>240.1</v>
+        <v>239.07</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -10852,11 +10852,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>241.06</v>
+        <v>242.92</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -10907,11 +10907,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>239.07</v>
+        <v>242.65</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -10962,11 +10962,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>242.92</v>
+        <v>239.86</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -11017,11 +11017,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>242.65</v>
+        <v>244.88</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -11072,11 +11072,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>239.86</v>
+        <v>244.65</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -11127,11 +11127,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>244.88</v>
+        <v>244.79</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -11182,11 +11182,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>244.65</v>
+        <v>241.01</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -11237,11 +11237,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>244.79</v>
+        <v>245</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -11292,11 +11292,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>241.01</v>
+        <v>240</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -11347,11 +11347,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>245</v>
+        <v>242.54</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -11402,11 +11402,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>240</v>
+        <v>243.64</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -11457,11 +11457,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>242.54</v>
+        <v>244.57</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -11512,11 +11512,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>243.64</v>
+        <v>242</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -11567,11 +11567,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>244.57</v>
+        <v>242.33</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -11622,11 +11622,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>242</v>
+        <v>242.58</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -11677,11 +11677,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>242.33</v>
+        <v>242.46</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -11732,11 +11732,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>242.58</v>
+        <v>238.81</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -11787,11 +11787,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>242.46</v>
+        <v>238.88</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -11842,11 +11842,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>238.81</v>
+        <v>239.57</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -11897,11 +11897,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>238.88</v>
+        <v>239.55</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -11952,11 +11952,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>239.57</v>
+        <v>240</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -12007,11 +12007,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>239.55</v>
+        <v>237.58</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -12062,11 +12062,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>240</v>
+        <v>236.97</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -12117,11 +12117,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>237.58</v>
+        <v>238.73</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -12172,11 +12172,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>236.97</v>
+        <v>235</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -12227,11 +12227,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>238.73</v>
+        <v>232</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -12282,11 +12282,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>235</v>
+        <v>232.94</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -12337,11 +12337,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>232</v>
+        <v>233.67</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -12392,11 +12392,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>232.94</v>
+        <v>233</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -12447,11 +12447,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>233.67</v>
+        <v>230.01</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -12502,11 +12502,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>233</v>
+        <v>229.81</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -12557,11 +12557,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>230.01</v>
+        <v>231.73</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -12612,11 +12612,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229.81</v>
+        <v>229.62</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -12667,11 +12667,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>231.73</v>
+        <v>231</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -12722,11 +12722,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>229.62</v>
+        <v>230.87</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -12777,11 +12777,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>231</v>
+        <v>234.36</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -12832,11 +12832,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>230.87</v>
+        <v>236</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -12887,11 +12887,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>234.36</v>
+        <v>239.75</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -12942,11 +12942,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>236</v>
+        <v>239.86</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -12997,11 +12997,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>239.75</v>
+        <v>239.31</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -13052,11 +13052,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>239.86</v>
+        <v>237.86</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -13107,11 +13107,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>239.31</v>
+        <v>237.51</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -13162,11 +13162,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>237.86</v>
+        <v>229.72</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -13217,11 +13217,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>237.51</v>
+        <v>229.63</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -13272,11 +13272,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>229.72</v>
+        <v>230</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -13327,11 +13327,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>229.63</v>
+        <v>233.76</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -13382,11 +13382,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>230</v>
+        <v>232.7</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -13437,11 +13437,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>233.76</v>
+        <v>235.51</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -13492,11 +13492,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>232.7</v>
+        <v>229.19</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -13547,11 +13547,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>235.51</v>
+        <v>228.66</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -13602,11 +13602,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>229.19</v>
+        <v>227.02</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -13657,11 +13657,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>228.66</v>
+        <v>228.34</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -13712,11 +13712,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>227.02</v>
+        <v>226.95</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -13767,11 +13767,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>228.34</v>
+        <v>225.38</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -13822,11 +13822,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>226.95</v>
+        <v>224.95</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -13877,11 +13877,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>225.38</v>
+        <v>223.27</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -13932,11 +13932,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>224.95</v>
+        <v>221</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -13987,11 +13987,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>223.27</v>
+        <v>220</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -14042,11 +14042,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>221</v>
+        <v>218.95</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -14097,11 +14097,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>220</v>
+        <v>216.72</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -14152,11 +14152,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>218.95</v>
+        <v>215.72</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -14207,11 +14207,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>216.72</v>
+        <v>207.73</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -14262,11 +14262,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>215.72</v>
+        <v>209.9</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -14317,11 +14317,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>207.73</v>
+        <v>208.02</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -14372,11 +14372,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>209.9</v>
+        <v>218.17</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -14427,11 +14427,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>208.02</v>
+        <v>215</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -14482,11 +14482,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>218.17</v>
+        <v>216.78</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -14537,11 +14537,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>215</v>
+        <v>220.11</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -14592,11 +14592,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>216.78</v>
+        <v>224.02</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -14647,11 +14647,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>220.11</v>
+        <v>222</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -14702,11 +14702,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>224.02</v>
+        <v>226.29</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -14757,11 +14757,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>222</v>
+        <v>229.78</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -14812,11 +14812,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>226.29</v>
+        <v>230.07</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -14867,11 +14867,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>229.78</v>
+        <v>228</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -14922,11 +14922,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>230.07</v>
+        <v>229</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -14977,11 +14977,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>228</v>
+        <v>228.47</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -15032,11 +15032,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>229</v>
+        <v>227.89</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -15087,11 +15087,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>228.47</v>
+        <v>227.96</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -15142,11 +15142,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>227.89</v>
+        <v>228.86</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -15197,11 +15197,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>227.96</v>
+        <v>228.74</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -15252,11 +15252,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>228.86</v>
+        <v>229.53</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -15307,11 +15307,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>228.74</v>
+        <v>229.54</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -15362,11 +15362,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>229.53</v>
+        <v>228.98</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -15417,11 +15417,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>229.54</v>
+        <v>230.59</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -15472,11 +15472,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>228.98</v>
+        <v>231.86</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -15527,11 +15527,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>230.59</v>
+        <v>232</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -15582,11 +15582,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>231.86</v>
+        <v>232</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -15637,11 +15637,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>232</v>
+        <v>228.35</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -15692,11 +15692,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>232</v>
+        <v>231.72</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -15747,11 +15747,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>228.35</v>
+        <v>232.29</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -15802,11 +15802,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>231.72</v>
+        <v>233</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -15857,11 +15857,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>232.29</v>
+        <v>231.55</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -15912,11 +15912,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>233</v>
+        <v>234.02</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -15967,11 +15967,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>231.55</v>
+        <v>232.43</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -16022,11 +16022,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>234.02</v>
+        <v>232.19</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -16077,11 +16077,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>232.43</v>
+        <v>232.37</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -16132,11 +16132,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>232.19</v>
+        <v>231.83</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -16187,11 +16187,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>232.37</v>
+        <v>234.7</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -16242,11 +16242,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>231.83</v>
+        <v>234</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -16297,11 +16297,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>234.7</v>
+        <v>236</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -16352,11 +16352,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -16407,11 +16407,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>236</v>
+        <v>236.85</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -16462,11 +16462,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>235</v>
+        <v>239.74</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -16517,11 +16517,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>236.85</v>
+        <v>237.29</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -16572,11 +16572,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>239.74</v>
+        <v>239.91</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -16627,11 +16627,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>237.29</v>
+        <v>242.92</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -16682,11 +16682,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>239.91</v>
+        <v>243</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -16737,11 +16737,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>242.92</v>
+        <v>241.53</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -16792,11 +16792,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>243</v>
+        <v>245.8</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -16847,11 +16847,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>241.53</v>
+        <v>249</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -16902,11 +16902,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>245.8</v>
+        <v>240.83</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -16957,11 +16957,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>249</v>
+        <v>246.94</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -17012,11 +17012,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>240.83</v>
+        <v>244.6</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -17067,11 +17067,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>246.94</v>
+        <v>243.29</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -17122,11 +17122,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>244.6</v>
+        <v>242.17</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -17177,11 +17177,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>243.29</v>
+        <v>240</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -17232,11 +17232,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>242.17</v>
+        <v>239.92</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -17287,11 +17287,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>240</v>
+        <v>234.66</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -17342,11 +17342,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>239.92</v>
+        <v>234.83</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -17397,11 +17397,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>234.66</v>
+        <v>235.07</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -17452,11 +17452,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>234.83</v>
+        <v>235.01</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -17507,11 +17507,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>235.07</v>
+        <v>234.09</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -17562,11 +17562,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>235.01</v>
+        <v>235.16</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -17617,11 +17617,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>234.09</v>
+        <v>236</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -17672,11 +17672,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>235.16</v>
+        <v>233.94</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -17727,11 +17727,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>236</v>
+        <v>234.91</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -17782,11 +17782,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>233.94</v>
+        <v>237.15</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -17837,11 +17837,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>234.91</v>
+        <v>238</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -17892,11 +17892,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>237.15</v>
+        <v>244.9</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -17947,11 +17947,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>238</v>
+        <v>245.53</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -18002,11 +18002,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>244.9</v>
+        <v>245.78</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -18057,11 +18057,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>245.53</v>
+        <v>245.19</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -18112,11 +18112,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>245.78</v>
+        <v>248.28</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -18167,11 +18167,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>245.19</v>
+        <v>247.94</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -18222,11 +18222,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>248.28</v>
+        <v>248</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -18277,11 +18277,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>247.94</v>
+        <v>248</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -18332,11 +18332,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>248</v>
+        <v>248.13</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -18387,11 +18387,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>248</v>
+        <v>247.99</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -18442,11 +18442,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>248.13</v>
+        <v>246</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -18497,11 +18497,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>247.99</v>
+        <v>246.26</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -18607,11 +18607,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>246.26</v>
+        <v>246</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -18662,11 +18662,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>246</v>
+        <v>247.26</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -18717,11 +18717,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>246</v>
+        <v>254.35</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -18772,11 +18772,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>247.26</v>
+        <v>256.31</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -18827,11 +18827,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>254.35</v>
+        <v>255.67</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -18882,11 +18882,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>256.31</v>
+        <v>255.2</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -18937,11 +18937,11 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>255.67</v>
+        <v>255</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -18992,11 +18992,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>255.2</v>
+        <v>256</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -19047,11 +19047,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>255</v>
+        <v>255.72</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -19102,11 +19102,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>256</v>
+        <v>258.2</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -19157,11 +19157,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>255.72</v>
+        <v>259.77</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -19212,11 +19212,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>258.2</v>
+        <v>259.81</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -19267,11 +19267,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>259.77</v>
+        <v>259.8</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -19322,11 +19322,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>259.81</v>
+        <v>262.97</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -19377,11 +19377,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>259.8</v>
+        <v>264.85</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -19432,11 +19432,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>262.97</v>
+        <v>264.85</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -19487,11 +19487,11 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>264.85</v>
+        <v>262.5</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -19542,11 +19542,11 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>264.85</v>
+        <v>263.99</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -19597,11 +19597,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>262.5</v>
+        <v>264.12</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -19652,11 +19652,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>263.99</v>
+        <v>259.93</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -19707,11 +19707,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>264.12</v>
+        <v>258.66</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -19762,11 +19762,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>259.93</v>
+        <v>252.68</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -19817,11 +19817,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>258.66</v>
+        <v>255</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -19872,11 +19872,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>252.68</v>
+        <v>256.79</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -19982,11 +19982,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>256.79</v>
+        <v>254.65</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -20037,11 +20037,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>255</v>
+        <v>255.93</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -20092,11 +20092,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>254.65</v>
+        <v>257.05</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -20147,11 +20147,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>255.93</v>
+        <v>257.62</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -20202,11 +20202,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>257.05</v>
+        <v>253.39</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -20257,11 +20257,11 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>257.62</v>
+        <v>255.01</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -20312,11 +20312,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>253.39</v>
+        <v>255</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -20367,11 +20367,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>255.01</v>
+        <v>255.96</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -20422,11 +20422,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -20477,11 +20477,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>255.96</v>
+        <v>253</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -20532,11 +20532,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>254</v>
+        <v>259.45</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -20587,11 +20587,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -20642,11 +20642,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>259.45</v>
+        <v>260</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -20697,11 +20697,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>260</v>
+        <v>259.92</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -20752,11 +20752,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -20807,11 +20807,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>259.92</v>
+        <v>259.2</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -20862,11 +20862,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -20917,11 +20917,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>259.2</v>
+        <v>256</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -20972,11 +20972,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>253</v>
+        <v>255.34</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -21027,11 +21027,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>256</v>
+        <v>254.91</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -21082,11 +21082,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>255.34</v>
+        <v>244.83</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -21137,11 +21137,11 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>254.91</v>
+        <v>248</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -21192,11 +21192,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>244.83</v>
+        <v>247.63</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -21247,11 +21247,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>248</v>
+        <v>244.24</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -21302,11 +21302,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>247.63</v>
+        <v>239.2</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -21357,11 +21357,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>244.24</v>
+        <v>239.36</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -21412,11 +21412,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>239.2</v>
+        <v>236.72</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -21467,11 +21467,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>239.36</v>
+        <v>234.18</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -21522,11 +21522,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>236.72</v>
+        <v>231.38</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -21577,11 +21577,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>234.18</v>
+        <v>230.14</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -21632,11 +21632,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>231.38</v>
+        <v>230.59</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -21687,11 +21687,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>230.14</v>
+        <v>230.87</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -21742,11 +21742,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>230.59</v>
+        <v>228.39</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -21797,11 +21797,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>230.87</v>
+        <v>228</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -21852,11 +21852,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>228.39</v>
+        <v>231</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -21907,11 +21907,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>228</v>
+        <v>232.86</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -21962,11 +21962,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>231</v>
+        <v>233.12</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -22017,11 +22017,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>232.86</v>
+        <v>234.29</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -22072,11 +22072,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>233.12</v>
+        <v>234.94</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -22127,11 +22127,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>234.29</v>
+        <v>235.13</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -22182,11 +22182,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>234.94</v>
+        <v>235.25</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -22237,11 +22237,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>235.13</v>
+        <v>235.09</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -22292,11 +22292,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>235.25</v>
+        <v>235.17</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -22347,11 +22347,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>235.09</v>
+        <v>230.48</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -22402,11 +22402,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>235.17</v>
+        <v>228.65</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -22457,11 +22457,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>230.48</v>
+        <v>225.78</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -22512,11 +22512,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>228.65</v>
+        <v>225.73</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -22567,11 +22567,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>225.78</v>
+        <v>225.18</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -22622,11 +22622,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>225.73</v>
+        <v>225.3</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -22677,11 +22677,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>225.18</v>
+        <v>224.37</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -22732,11 +22732,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>225.3</v>
+        <v>218</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -22787,11 +22787,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>224.37</v>
+        <v>218.2</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -22842,11 +22842,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>218</v>
+        <v>219.23</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -22897,11 +22897,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>218.2</v>
+        <v>219.56</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -22952,11 +22952,11 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>219.23</v>
+        <v>220.8</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -23007,11 +23007,11 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>219.56</v>
+        <v>220</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -23062,11 +23062,11 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>220.8</v>
+        <v>217.91</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -23117,11 +23117,11 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -23172,11 +23172,11 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>217.91</v>
+        <v>217.12</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -23227,11 +23227,11 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>218</v>
+        <v>220.13</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -23282,11 +23282,11 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>217.12</v>
+        <v>218</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -23337,11 +23337,11 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>220.13</v>
+        <v>218</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -23392,11 +23392,11 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>218</v>
+        <v>222.78</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -23447,11 +23447,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>218</v>
+        <v>222.32</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -23502,11 +23502,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>222.78</v>
+        <v>222.11</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -23557,11 +23557,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>222.32</v>
+        <v>221.06</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -23612,11 +23612,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>222.11</v>
+        <v>222</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -23667,11 +23667,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>221.06</v>
+        <v>221.03</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -23722,11 +23722,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>222</v>
+        <v>220.62</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -23777,11 +23777,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>221.03</v>
+        <v>220.71</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -23832,11 +23832,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>220.62</v>
+        <v>218.73</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -23887,11 +23887,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>220.71</v>
+        <v>220.16</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -23942,11 +23942,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>218.73</v>
+        <v>218.99</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -23997,11 +23997,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>220.16</v>
+        <v>218</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -24052,11 +24052,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>218.99</v>
+        <v>218.98</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -24107,11 +24107,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>218</v>
+        <v>220.71</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -24162,11 +24162,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>218.98</v>
+        <v>221.77</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -24217,11 +24217,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>220.71</v>
+        <v>224.46</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -24272,11 +24272,11 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>221.77</v>
+        <v>227.29</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -24304,61 +24304,6 @@
         </is>
       </c>
       <c r="K434" t="inlineStr">
-        <is>
-          <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>vacuno_vivo_us</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Vacuno de sacrificio, vivo (EE. UU., 5 zonas)</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="E435" t="n">
-        <v>224.46</v>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>cwt</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="I435" t="inlineStr">
-        <is>
-          <t>USDA AMS Livestock Mandatory Reporting (LMR), Market News datamart</t>
-        </is>
-      </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>US-PD</t>
-        </is>
-      </c>
-      <c r="K435" t="inlineStr">
         <is>
           <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
         </is>
@@ -24450,7 +24395,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
     </row>
@@ -24462,7 +24407,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -24473,7 +24418,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -24568,7 +24513,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/vacuno_vivo_us.xlsx
+++ b/data/pack/us/vacuno_vivo_us.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K434"/>
+  <dimension ref="A1:K433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,11 +512,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>186</v>
+        <v>187.84</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -567,11 +567,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185.99</v>
+        <v>187</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>187.56</v>
+        <v>186.97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>187.84</v>
+        <v>186.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>187</v>
+        <v>190.14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>186.97</v>
+        <v>190.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>186.5</v>
+        <v>189.47</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -897,11 +897,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>190.14</v>
+        <v>189.92</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -952,11 +952,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>190.18</v>
+        <v>189.88</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1007,11 +1007,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>189.47</v>
+        <v>190.11</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>189.92</v>
+        <v>188.24</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>189.88</v>
+        <v>186</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1172,11 +1172,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>190.11</v>
+        <v>184</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>188.24</v>
+        <v>186.78</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1282,11 +1282,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>186</v>
+        <v>186.55</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1337,11 +1337,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>184</v>
+        <v>185.51</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>186.78</v>
+        <v>184.84</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1447,11 +1447,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>186.55</v>
+        <v>184.71</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1502,11 +1502,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185.51</v>
+        <v>184.95</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1557,11 +1557,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>184.84</v>
+        <v>184.97</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1612,11 +1612,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>184.71</v>
+        <v>185.71</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>184.95</v>
+        <v>187.12</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1722,11 +1722,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>184.97</v>
+        <v>187.87</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1777,11 +1777,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185.71</v>
+        <v>186.39</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1832,11 +1832,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>187.12</v>
+        <v>190.05</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1887,11 +1887,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>187.87</v>
+        <v>190</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>186.39</v>
+        <v>190</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1997,11 +1997,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>190.05</v>
+        <v>190</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2052,11 +2052,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>190</v>
+        <v>190.07</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>190</v>
+        <v>190.28</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2162,11 +2162,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>190</v>
+        <v>191.32</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>190.07</v>
+        <v>190.95</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2272,11 +2272,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>190.28</v>
+        <v>190.88</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>191.32</v>
+        <v>193.88</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2382,11 +2382,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>190.95</v>
+        <v>195.05</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>190.88</v>
+        <v>194.66</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2492,11 +2492,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>193.88</v>
+        <v>195.29</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2547,11 +2547,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>195.05</v>
+        <v>191.43</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>194.66</v>
+        <v>194.78</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>195.29</v>
+        <v>194.67</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2712,11 +2712,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>191.43</v>
+        <v>193.14</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2767,11 +2767,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>194.78</v>
+        <v>190.91</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2822,11 +2822,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>194.67</v>
+        <v>190.55</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2877,11 +2877,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>193.14</v>
+        <v>194.71</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>190.91</v>
+        <v>192</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2987,11 +2987,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>190.55</v>
+        <v>193.46</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3042,11 +3042,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>194.71</v>
+        <v>196.9</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>192</v>
+        <v>199.58</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3152,11 +3152,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>193.46</v>
+        <v>199.84</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3207,11 +3207,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>196.9</v>
+        <v>196.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3262,11 +3262,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>199.58</v>
+        <v>199.64</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3317,11 +3317,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>199.84</v>
+        <v>202.43</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>196.5</v>
+        <v>202.15</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3427,11 +3427,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>199.64</v>
+        <v>202.93</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3482,11 +3482,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>202.43</v>
+        <v>203.92</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3537,11 +3537,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>202.15</v>
+        <v>201.37</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3592,11 +3592,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>202.93</v>
+        <v>203.76</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>203.92</v>
+        <v>203.91</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3702,11 +3702,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>201.37</v>
+        <v>201</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3757,11 +3757,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>203.76</v>
+        <v>201.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3812,11 +3812,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>203.91</v>
+        <v>203.38</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3867,11 +3867,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>201</v>
+        <v>206.65</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>201.2</v>
+        <v>210.36</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3977,11 +3977,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>203.38</v>
+        <v>203</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>206.65</v>
+        <v>202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4087,11 +4087,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>210.36</v>
+        <v>208.8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4142,11 +4142,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>203</v>
+        <v>209.16</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>202</v>
+        <v>209.92</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4252,11 +4252,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>208.8</v>
+        <v>208</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4307,11 +4307,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>209.16</v>
+        <v>206.85</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4362,11 +4362,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>209.92</v>
+        <v>206.98</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4417,11 +4417,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>208</v>
+        <v>205.11</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>206.85</v>
+        <v>204</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4527,11 +4527,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>206.98</v>
+        <v>202.97</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4582,11 +4582,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>205.11</v>
+        <v>202.81</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4637,11 +4637,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>204</v>
+        <v>202.82</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -4747,11 +4747,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>202.81</v>
+        <v>203</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4802,11 +4802,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>202.82</v>
+        <v>200</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>202.97</v>
+        <v>200</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4912,11 +4912,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>203</v>
+        <v>199.54</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4967,11 +4967,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>200</v>
+        <v>199.46</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5077,11 +5077,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>199.54</v>
+        <v>198</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5132,11 +5132,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>199.46</v>
+        <v>197.58</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5187,11 +5187,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5242,11 +5242,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>198</v>
+        <v>196.38</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>197.58</v>
+        <v>196.41</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5352,11 +5352,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>195</v>
+        <v>196.84</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5407,11 +5407,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>196.38</v>
+        <v>201.09</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>196.41</v>
+        <v>199.59</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5517,11 +5517,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>196.84</v>
+        <v>200</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>201.09</v>
+        <v>205.04</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>199.59</v>
+        <v>202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5682,11 +5682,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>200</v>
+        <v>209.42</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5737,11 +5737,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>205.04</v>
+        <v>212.49</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5792,11 +5792,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>202</v>
+        <v>207.78</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5847,11 +5847,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>209.42</v>
+        <v>212.21</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5902,11 +5902,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>212.49</v>
+        <v>212.23</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5957,11 +5957,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>207.78</v>
+        <v>211.83</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -6012,11 +6012,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>212.21</v>
+        <v>210</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -6067,11 +6067,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>212.23</v>
+        <v>210</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6122,11 +6122,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>211.83</v>
+        <v>211.96</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6177,11 +6177,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>210</v>
+        <v>210.04</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6232,11 +6232,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>210</v>
+        <v>204.25</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6287,11 +6287,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>211.96</v>
+        <v>207.58</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6342,11 +6342,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>210.04</v>
+        <v>207.5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6397,11 +6397,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>204.25</v>
+        <v>207.57</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6452,11 +6452,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>207.58</v>
+        <v>206.79</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6507,11 +6507,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>207.5</v>
+        <v>208</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6562,11 +6562,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>207.57</v>
+        <v>208</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6617,11 +6617,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>206.79</v>
+        <v>211.19</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>208</v>
+        <v>212.28</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>208</v>
+        <v>208.52</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6782,11 +6782,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>211.19</v>
+        <v>212.55</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6837,11 +6837,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>212.28</v>
+        <v>210.08</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6892,11 +6892,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>208.52</v>
+        <v>216.03</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6947,11 +6947,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>212.55</v>
+        <v>214.23</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -7002,11 +7002,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>210.08</v>
+        <v>220.65</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -7057,11 +7057,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>216.03</v>
+        <v>221.2</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -7112,11 +7112,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>214.23</v>
+        <v>219.25</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -7167,11 +7167,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220.65</v>
+        <v>219.08</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -7222,11 +7222,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221.2</v>
+        <v>218.47</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -7277,11 +7277,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219.25</v>
+        <v>219.97</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -7332,11 +7332,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219.08</v>
+        <v>226.36</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -7387,11 +7387,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>218.47</v>
+        <v>226.56</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -7442,11 +7442,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219.97</v>
+        <v>225</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -7497,11 +7497,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>226.36</v>
+        <v>227.25</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -7552,11 +7552,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>226.56</v>
+        <v>225.93</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -7607,11 +7607,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>225</v>
+        <v>226.39</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -7662,11 +7662,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>227.25</v>
+        <v>219</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -7717,11 +7717,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>225.93</v>
+        <v>219</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -7772,11 +7772,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>226.39</v>
+        <v>230</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -7827,11 +7827,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219</v>
+        <v>230.05</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -7882,11 +7882,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219</v>
+        <v>223.15</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -7937,11 +7937,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>230</v>
+        <v>229.84</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>230.05</v>
+        <v>220.83</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -8047,11 +8047,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>223.15</v>
+        <v>229.25</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -8102,11 +8102,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229.84</v>
+        <v>234.35</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -8157,11 +8157,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220.83</v>
+        <v>230</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -8212,11 +8212,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229.25</v>
+        <v>236</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -8267,11 +8267,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>234.35</v>
+        <v>226.85</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -8322,11 +8322,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>230</v>
+        <v>237.04</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -8377,11 +8377,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>236</v>
+        <v>239.51</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -8432,11 +8432,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>226.85</v>
+        <v>236.43</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -8487,11 +8487,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>237.04</v>
+        <v>234.76</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -8542,11 +8542,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>239.51</v>
+        <v>237.19</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -8597,11 +8597,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>236.43</v>
+        <v>237.11</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -8652,11 +8652,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>234.76</v>
+        <v>240.13</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -8707,11 +8707,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>237.19</v>
+        <v>239.47</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -8762,11 +8762,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>237.11</v>
+        <v>233.17</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -8817,11 +8817,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>240.13</v>
+        <v>236.42</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -8872,11 +8872,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>239.47</v>
+        <v>235.55</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -8927,11 +8927,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>233.17</v>
+        <v>231.54</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -8982,11 +8982,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>236.42</v>
+        <v>230.08</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -9037,11 +9037,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>235.55</v>
+        <v>230.49</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -9092,11 +9092,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>231.54</v>
+        <v>227.19</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -9147,11 +9147,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>230.08</v>
+        <v>231.07</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -9202,11 +9202,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>230.49</v>
+        <v>231.99</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>227.19</v>
+        <v>222.55</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -9312,11 +9312,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>231.07</v>
+        <v>229.11</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -9367,11 +9367,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>231.99</v>
+        <v>229.66</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -9422,11 +9422,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>222.55</v>
+        <v>225.28</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -9477,11 +9477,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>229.11</v>
+        <v>235.08</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -9532,11 +9532,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229.66</v>
+        <v>237.52</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -9587,11 +9587,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>225.28</v>
+        <v>234</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -9642,11 +9642,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>235.08</v>
+        <v>233.67</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -9697,11 +9697,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>237.52</v>
+        <v>233.77</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -9752,11 +9752,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>234</v>
+        <v>236.13</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -9807,11 +9807,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>233.67</v>
+        <v>239.19</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -9862,11 +9862,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>233.77</v>
+        <v>238.88</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -9917,11 +9917,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>236.13</v>
+        <v>230.28</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -9972,11 +9972,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>239.19</v>
+        <v>231.04</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -10027,11 +10027,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>238.88</v>
+        <v>239.36</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -10082,11 +10082,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>230.28</v>
+        <v>230</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -10137,11 +10137,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>231.04</v>
+        <v>240</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -10192,11 +10192,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>239.36</v>
+        <v>235.6</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -10247,11 +10247,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>230</v>
+        <v>242.38</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -10302,11 +10302,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>240</v>
+        <v>243.69</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -10357,11 +10357,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>235.6</v>
+        <v>240</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -10412,11 +10412,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>242.38</v>
+        <v>240</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -10467,11 +10467,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>243.69</v>
+        <v>237</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -10522,11 +10522,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>240</v>
+        <v>240.1</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -10577,11 +10577,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>240</v>
+        <v>241.06</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -10632,11 +10632,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>237</v>
+        <v>239.07</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -10687,11 +10687,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>240.1</v>
+        <v>242.92</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -10742,11 +10742,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>241.06</v>
+        <v>242.65</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -10797,11 +10797,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>239.07</v>
+        <v>239.86</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -10852,11 +10852,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>242.92</v>
+        <v>244.88</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -10907,11 +10907,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>242.65</v>
+        <v>244.65</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -10962,11 +10962,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>239.86</v>
+        <v>244.79</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -11017,11 +11017,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>244.88</v>
+        <v>241.01</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -11072,11 +11072,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>244.65</v>
+        <v>245</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -11127,11 +11127,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>244.79</v>
+        <v>240</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -11182,11 +11182,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>241.01</v>
+        <v>242.54</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -11237,11 +11237,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>245</v>
+        <v>243.64</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -11292,11 +11292,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>240</v>
+        <v>244.57</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -11347,11 +11347,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>242.54</v>
+        <v>242</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -11402,11 +11402,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>243.64</v>
+        <v>242.33</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -11457,11 +11457,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>244.57</v>
+        <v>242.58</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -11512,11 +11512,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>242</v>
+        <v>242.46</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -11567,11 +11567,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>242.33</v>
+        <v>238.81</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -11622,11 +11622,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>242.58</v>
+        <v>238.88</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -11677,11 +11677,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>242.46</v>
+        <v>239.57</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -11732,11 +11732,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>238.81</v>
+        <v>239.55</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -11787,11 +11787,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>238.88</v>
+        <v>240</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -11842,11 +11842,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>239.57</v>
+        <v>237.58</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -11897,11 +11897,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>239.55</v>
+        <v>236.97</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -11952,11 +11952,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>240</v>
+        <v>238.73</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -12007,11 +12007,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>237.58</v>
+        <v>235</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -12062,11 +12062,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>236.97</v>
+        <v>232</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -12117,11 +12117,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>238.73</v>
+        <v>232.94</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -12172,11 +12172,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>235</v>
+        <v>233.67</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -12227,11 +12227,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -12282,11 +12282,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>232.94</v>
+        <v>230.01</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -12337,11 +12337,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>233.67</v>
+        <v>229.81</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -12392,11 +12392,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>233</v>
+        <v>231.73</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -12447,11 +12447,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>230.01</v>
+        <v>229.62</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -12502,11 +12502,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>229.81</v>
+        <v>231</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -12557,11 +12557,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>231.73</v>
+        <v>230.87</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -12612,11 +12612,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229.62</v>
+        <v>234.36</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -12667,11 +12667,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -12722,11 +12722,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>230.87</v>
+        <v>239.75</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -12777,11 +12777,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>234.36</v>
+        <v>239.86</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -12832,11 +12832,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>236</v>
+        <v>239.31</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -12887,11 +12887,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>239.75</v>
+        <v>237.86</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -12942,11 +12942,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>239.86</v>
+        <v>237.51</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -12997,11 +12997,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>239.31</v>
+        <v>229.72</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -13052,11 +13052,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>237.86</v>
+        <v>229.63</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -13107,11 +13107,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>237.51</v>
+        <v>230</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -13162,11 +13162,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>229.72</v>
+        <v>233.76</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -13217,11 +13217,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>229.63</v>
+        <v>232.7</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -13272,11 +13272,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>230</v>
+        <v>235.51</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -13327,11 +13327,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>233.76</v>
+        <v>229.19</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -13382,11 +13382,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>232.7</v>
+        <v>228.66</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -13437,11 +13437,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>235.51</v>
+        <v>227.02</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -13492,11 +13492,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>229.19</v>
+        <v>228.34</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -13547,11 +13547,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>228.66</v>
+        <v>226.95</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -13602,11 +13602,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>227.02</v>
+        <v>225.38</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -13657,11 +13657,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>228.34</v>
+        <v>224.95</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -13712,11 +13712,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>226.95</v>
+        <v>223.27</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -13767,11 +13767,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>225.38</v>
+        <v>221</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -13822,11 +13822,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>224.95</v>
+        <v>220</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -13877,11 +13877,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>223.27</v>
+        <v>218.95</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -13932,11 +13932,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>221</v>
+        <v>216.72</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -13987,11 +13987,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>220</v>
+        <v>215.72</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -14042,11 +14042,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>218.95</v>
+        <v>207.73</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -14097,11 +14097,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>216.72</v>
+        <v>209.9</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -14152,11 +14152,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>215.72</v>
+        <v>208.02</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -14207,11 +14207,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>207.73</v>
+        <v>218.17</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -14262,11 +14262,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>209.9</v>
+        <v>215</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -14317,11 +14317,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>208.02</v>
+        <v>216.78</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -14372,11 +14372,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>218.17</v>
+        <v>220.11</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -14427,11 +14427,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>215</v>
+        <v>224.02</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -14482,11 +14482,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>216.78</v>
+        <v>222</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -14537,11 +14537,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>220.11</v>
+        <v>226.29</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -14592,11 +14592,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>224.02</v>
+        <v>229.78</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -14647,11 +14647,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222</v>
+        <v>230.07</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -14702,11 +14702,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>226.29</v>
+        <v>228</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -14757,11 +14757,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>229.78</v>
+        <v>229</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -14812,11 +14812,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>230.07</v>
+        <v>228.47</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -14867,11 +14867,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>228</v>
+        <v>227.89</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -14922,11 +14922,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>229</v>
+        <v>227.96</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -14977,11 +14977,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>228.47</v>
+        <v>228.86</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -15032,11 +15032,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>227.89</v>
+        <v>228.74</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -15087,11 +15087,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>227.96</v>
+        <v>229.53</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -15142,11 +15142,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>228.86</v>
+        <v>229.54</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -15197,11 +15197,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>228.74</v>
+        <v>228.98</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -15252,11 +15252,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>229.53</v>
+        <v>230.59</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -15307,11 +15307,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>229.54</v>
+        <v>231.86</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -15362,11 +15362,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>228.98</v>
+        <v>232</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -15417,11 +15417,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>230.59</v>
+        <v>232</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -15472,11 +15472,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>231.86</v>
+        <v>228.35</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -15527,11 +15527,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>232</v>
+        <v>231.72</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -15582,11 +15582,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>232</v>
+        <v>232.29</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -15637,11 +15637,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>228.35</v>
+        <v>233</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -15692,11 +15692,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>231.72</v>
+        <v>231.55</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -15747,11 +15747,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>232.29</v>
+        <v>234.02</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -15802,11 +15802,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>233</v>
+        <v>232.43</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -15857,11 +15857,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>231.55</v>
+        <v>232.19</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -15912,11 +15912,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>234.02</v>
+        <v>232.37</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -15967,11 +15967,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>232.43</v>
+        <v>231.83</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -16022,11 +16022,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>232.19</v>
+        <v>234.7</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -16077,11 +16077,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>232.37</v>
+        <v>234</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -16132,11 +16132,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>231.83</v>
+        <v>236</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -16187,11 +16187,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>234.7</v>
+        <v>235</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -16242,11 +16242,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>234</v>
+        <v>236.85</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -16297,11 +16297,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>236</v>
+        <v>239.74</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -16352,11 +16352,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>235</v>
+        <v>237.29</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -16407,11 +16407,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>236.85</v>
+        <v>239.91</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -16462,11 +16462,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>239.74</v>
+        <v>242.92</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -16517,11 +16517,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>237.29</v>
+        <v>243</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -16572,11 +16572,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>239.91</v>
+        <v>241.53</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -16627,11 +16627,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>242.92</v>
+        <v>245.8</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -16682,11 +16682,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -16737,11 +16737,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>241.53</v>
+        <v>240.83</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -16792,11 +16792,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>245.8</v>
+        <v>246.94</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -16847,11 +16847,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>249</v>
+        <v>244.6</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -16902,11 +16902,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>240.83</v>
+        <v>243.29</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -16957,11 +16957,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>246.94</v>
+        <v>242.17</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -17012,11 +17012,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>244.6</v>
+        <v>240</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -17067,11 +17067,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>243.29</v>
+        <v>239.92</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -17122,11 +17122,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>242.17</v>
+        <v>234.66</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -17177,11 +17177,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>240</v>
+        <v>234.83</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -17232,11 +17232,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>239.92</v>
+        <v>235.07</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -17287,11 +17287,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>234.66</v>
+        <v>235.01</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -17342,11 +17342,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>234.83</v>
+        <v>234.09</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -17397,11 +17397,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>235.07</v>
+        <v>235.16</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -17452,11 +17452,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>235.01</v>
+        <v>236</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -17507,11 +17507,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>234.09</v>
+        <v>233.94</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -17562,11 +17562,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>235.16</v>
+        <v>234.91</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -17617,11 +17617,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>236</v>
+        <v>237.15</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -17672,11 +17672,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>233.94</v>
+        <v>238</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -17727,11 +17727,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>234.91</v>
+        <v>244.9</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -17782,11 +17782,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>237.15</v>
+        <v>245.53</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -17837,11 +17837,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>238</v>
+        <v>245.78</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -17892,11 +17892,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>244.9</v>
+        <v>245.19</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -17947,11 +17947,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>245.53</v>
+        <v>248.28</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -18002,11 +18002,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>245.78</v>
+        <v>247.94</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -18057,11 +18057,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>245.19</v>
+        <v>248</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -18112,11 +18112,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>248.28</v>
+        <v>248</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -18167,11 +18167,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>247.94</v>
+        <v>248.13</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -18222,11 +18222,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>248</v>
+        <v>247.99</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -18277,11 +18277,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -18332,11 +18332,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>248.13</v>
+        <v>246.26</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -18387,11 +18387,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>247.99</v>
+        <v>246</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -18497,11 +18497,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>246.26</v>
+        <v>247.26</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -18552,11 +18552,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>246</v>
+        <v>254.35</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -18607,11 +18607,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>246</v>
+        <v>256.31</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -18662,11 +18662,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>247.26</v>
+        <v>255.67</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -18717,11 +18717,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>254.35</v>
+        <v>255.2</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -18772,11 +18772,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>256.31</v>
+        <v>255</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -18827,11 +18827,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>255.67</v>
+        <v>256</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -18882,11 +18882,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>255.2</v>
+        <v>255.72</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -18937,11 +18937,11 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>255</v>
+        <v>258.2</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -18992,11 +18992,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>256</v>
+        <v>259.77</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -19047,11 +19047,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>255.72</v>
+        <v>259.81</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -19102,11 +19102,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>258.2</v>
+        <v>259.8</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -19157,11 +19157,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>259.77</v>
+        <v>262.97</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -19212,11 +19212,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>259.81</v>
+        <v>264.85</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -19267,11 +19267,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>259.8</v>
+        <v>264.85</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -19322,11 +19322,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>262.97</v>
+        <v>262.5</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -19377,11 +19377,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>264.85</v>
+        <v>263.99</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -19432,11 +19432,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>264.85</v>
+        <v>264.12</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -19487,11 +19487,11 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>262.5</v>
+        <v>259.93</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -19542,11 +19542,11 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>263.99</v>
+        <v>258.66</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -19597,11 +19597,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>264.12</v>
+        <v>252.68</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -19652,11 +19652,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>259.93</v>
+        <v>255</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -19707,11 +19707,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>258.66</v>
+        <v>256.79</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -19762,11 +19762,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>252.68</v>
+        <v>255</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -19817,11 +19817,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>255</v>
+        <v>254.65</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -19872,11 +19872,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>256.79</v>
+        <v>255.93</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -19927,11 +19927,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>255</v>
+        <v>257.05</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -19982,11 +19982,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>254.65</v>
+        <v>257.62</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -20037,11 +20037,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>255.93</v>
+        <v>253.39</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -20092,11 +20092,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>257.05</v>
+        <v>255.01</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -20147,11 +20147,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>257.62</v>
+        <v>255</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -20202,11 +20202,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>253.39</v>
+        <v>255.96</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -20257,11 +20257,11 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>255.01</v>
+        <v>254</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -20312,11 +20312,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -20367,11 +20367,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>255.96</v>
+        <v>259.45</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -20422,11 +20422,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -20477,11 +20477,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -20532,11 +20532,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>259.45</v>
+        <v>259.92</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -20587,11 +20587,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -20642,11 +20642,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>260</v>
+        <v>259.2</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -20697,11 +20697,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>259.92</v>
+        <v>253</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -20752,11 +20752,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -20807,11 +20807,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>259.2</v>
+        <v>255.34</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -20862,11 +20862,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>253</v>
+        <v>254.91</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -20917,11 +20917,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>256</v>
+        <v>244.83</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -20972,11 +20972,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>255.34</v>
+        <v>248</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -21027,11 +21027,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>254.91</v>
+        <v>247.63</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -21082,11 +21082,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>244.83</v>
+        <v>244.24</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -21137,11 +21137,11 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>248</v>
+        <v>239.2</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -21192,11 +21192,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>247.63</v>
+        <v>239.36</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -21247,11 +21247,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>244.24</v>
+        <v>236.72</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -21302,11 +21302,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>239.2</v>
+        <v>234.18</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -21357,11 +21357,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>239.36</v>
+        <v>231.38</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -21412,11 +21412,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>236.72</v>
+        <v>230.14</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -21467,11 +21467,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>234.18</v>
+        <v>230.59</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -21522,11 +21522,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>231.38</v>
+        <v>230.87</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -21577,11 +21577,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>230.14</v>
+        <v>228.39</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -21632,11 +21632,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>230.59</v>
+        <v>228</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -21687,11 +21687,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>230.87</v>
+        <v>231</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -21742,11 +21742,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>228.39</v>
+        <v>232.86</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -21797,11 +21797,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>228</v>
+        <v>233.12</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -21852,11 +21852,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>231</v>
+        <v>234.29</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -21907,11 +21907,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>232.86</v>
+        <v>234.94</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -21962,11 +21962,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>233.12</v>
+        <v>235.13</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -22017,11 +22017,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>234.29</v>
+        <v>235.25</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -22072,11 +22072,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>234.94</v>
+        <v>235.09</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -22127,11 +22127,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>235.13</v>
+        <v>235.17</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -22182,11 +22182,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>235.25</v>
+        <v>230.48</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -22237,11 +22237,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>235.09</v>
+        <v>228.65</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -22292,11 +22292,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>235.17</v>
+        <v>225.78</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -22347,11 +22347,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>230.48</v>
+        <v>225.73</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -22402,11 +22402,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>228.65</v>
+        <v>225.18</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -22457,11 +22457,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>225.78</v>
+        <v>225.3</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -22512,11 +22512,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>225.73</v>
+        <v>224.37</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -22567,11 +22567,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>225.18</v>
+        <v>218</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -22622,11 +22622,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>225.3</v>
+        <v>218.2</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -22677,11 +22677,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>224.37</v>
+        <v>219.23</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -22732,11 +22732,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>218</v>
+        <v>219.56</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -22787,11 +22787,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>218.2</v>
+        <v>220.8</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -22842,11 +22842,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>219.23</v>
+        <v>220</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -22897,11 +22897,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>219.56</v>
+        <v>217.91</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -22952,11 +22952,11 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>220.8</v>
+        <v>218</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -23007,11 +23007,11 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>220</v>
+        <v>217.12</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -23062,11 +23062,11 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>217.91</v>
+        <v>220.13</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -23172,11 +23172,11 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>217.12</v>
+        <v>218</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -23227,11 +23227,11 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>220.13</v>
+        <v>222.78</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -23282,11 +23282,11 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>218</v>
+        <v>222.32</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -23337,11 +23337,11 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>218</v>
+        <v>222.11</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -23392,11 +23392,11 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>222.78</v>
+        <v>221.06</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -23447,11 +23447,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>222.32</v>
+        <v>222</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -23502,11 +23502,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>222.11</v>
+        <v>221.03</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -23557,11 +23557,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>221.06</v>
+        <v>220.62</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -23612,11 +23612,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>222</v>
+        <v>220.71</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -23667,11 +23667,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>221.03</v>
+        <v>218.73</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -23722,11 +23722,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>220.62</v>
+        <v>220.16</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -23777,11 +23777,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>220.71</v>
+        <v>218.99</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -23832,11 +23832,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>218.73</v>
+        <v>218</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -23887,11 +23887,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>220.16</v>
+        <v>218.98</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -23942,11 +23942,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>218.99</v>
+        <v>220.71</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -23997,11 +23997,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>218</v>
+        <v>221.77</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -24052,11 +24052,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>218.98</v>
+        <v>224.46</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -24107,11 +24107,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>220.71</v>
+        <v>227.35</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -24162,11 +24162,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>221.77</v>
+        <v>222</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -24217,11 +24217,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>224.46</v>
+        <v>228.52</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -24249,61 +24249,6 @@
         </is>
       </c>
       <c r="K433" t="inlineStr">
-        <is>
-          <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>vacuno_vivo_us</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Vacuno de sacrificio, vivo (EE. UU., 5 zonas)</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="E434" t="n">
-        <v>227.29</v>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>cwt</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
-        <is>
-          <t>USDA AMS Livestock Mandatory Reporting (LMR), Market News datamart</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>US-PD</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr">
         <is>
           <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
         </is>
@@ -24395,7 +24340,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-21</t>
         </is>
       </c>
     </row>
@@ -24407,7 +24352,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -24418,7 +24363,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -24513,7 +24458,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/vacuno_vivo_us.xlsx
+++ b/data/pack/us/vacuno_vivo_us.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K433"/>
+  <dimension ref="A1:K434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24249,6 +24249,61 @@
         </is>
       </c>
       <c r="K433" t="inlineStr">
+        <is>
+          <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>vacuno_vivo_us</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Vacuno de sacrificio, vivo (EE. UU., 5 zonas)</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>224.04</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>cwt</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>USDA AMS Livestock Mandatory Reporting (LMR), Market News datamart</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
         <is>
           <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
         </is>
@@ -24352,7 +24407,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -24363,7 +24418,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -24458,7 +24513,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/vacuno_vivo_us.xlsx
+++ b/data/pack/us/vacuno_vivo_us.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K434"/>
+  <dimension ref="A1:K435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24304,6 +24304,61 @@
         </is>
       </c>
       <c r="K434" t="inlineStr">
+        <is>
+          <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>vacuno_vivo_us</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Vacuno de sacrificio, vivo (EE. UU., 5 zonas)</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>224</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>cwt</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>USDA AMS Livestock Mandatory Reporting (LMR), Market News datamart</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
         <is>
           <t>Source: U.S. Department of Agriculture, Agricultural Marketing Service (Livestock Mandatory Reporting)</t>
         </is>
@@ -24407,7 +24462,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -24418,7 +24473,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -24513,7 +24568,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
